--- a/data/Blumenau/Junho 2025 - Cooper.xlsx
+++ b/data/Blumenau/Junho 2025 - Cooper.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/10658dd111efd9f3/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://furb-my.sharepoint.com/personal/bttomio_furb_br/Documents/Documentos/GitHub/CidadaniaFinanceira/data/Blumenau/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{65A37C40-36B2-48CC-9058-F4C2CF86E6CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CA9DA28-DF2B-4026-9C8A-EDC804A0E5AF}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{65A37C40-36B2-48CC-9058-F4C2CF86E6CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B69F4189-2C80-47E6-86F9-5520B23703BC}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3D367209-BCF2-43D7-94CA-7CBD754B7C45}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{3D367209-BCF2-43D7-94CA-7CBD754B7C45}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="59">
   <si>
     <t>MERCADO</t>
   </si>
@@ -210,13 +210,16 @@
   </si>
   <si>
     <t>Caturra</t>
+  </si>
+  <si>
+    <t>Junho/2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -815,70 +818,70 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1216,7 +1219,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C664814C-C990-420F-84BC-925E701FFE60}">
   <dimension ref="A1:I32"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -1229,7 +1232,7 @@
     <col min="9" max="9" width="15.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.6">
+    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1240,7 +1243,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="5"/>
     </row>
-    <row r="2" spans="1:9" ht="15.6">
+    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -1251,7 +1254,7 @@
       <c r="H2" s="7"/>
       <c r="I2" s="10"/>
     </row>
-    <row r="3" spans="1:9" ht="15.6">
+    <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -1262,7 +1265,7 @@
       <c r="H3" s="7"/>
       <c r="I3" s="10"/>
     </row>
-    <row r="4" spans="1:9" ht="16.149999999999999" thickBot="1">
+    <row r="4" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11"/>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
@@ -1273,26 +1276,26 @@
       <c r="H4" s="12"/>
       <c r="I4" s="15"/>
     </row>
-    <row r="5" spans="1:9" ht="16.149999999999999" thickBot="1">
+    <row r="5" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="67" t="s">
+      <c r="B5" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="67"/>
+      <c r="C5" s="50"/>
       <c r="D5" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="68">
-        <v>45823</v>
-      </c>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
+      <c r="E5" s="71" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
       <c r="H5" s="18"/>
       <c r="I5" s="19"/>
     </row>
-    <row r="6" spans="1:9" ht="16.149999999999999" thickBot="1">
+    <row r="6" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="20" t="s">
         <v>3</v>
       </c>
@@ -1305,27 +1308,27 @@
       <c r="D6" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="69" t="s">
+      <c r="E6" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="71"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="53"/>
       <c r="I6" s="22" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.6">
-      <c r="A7" s="50" t="s">
+    <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="52" t="s">
+      <c r="B7" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="52" t="s">
+      <c r="C7" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="52">
+      <c r="D7" s="56">
         <v>5</v>
       </c>
       <c r="E7" s="23" t="s">
@@ -1338,15 +1341,15 @@
         <v>14</v>
       </c>
       <c r="H7" s="26"/>
-      <c r="I7" s="54">
+      <c r="I7" s="58">
         <v>5.4980000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16.149999999999999" thickBot="1">
-      <c r="A8" s="63"/>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
+    <row r="8" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="55"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
       <c r="E8" s="27" t="s">
         <v>15</v>
       </c>
@@ -1357,19 +1360,19 @@
         <v>27.99</v>
       </c>
       <c r="H8" s="30"/>
-      <c r="I8" s="56"/>
-    </row>
-    <row r="9" spans="1:9" ht="31.15">
-      <c r="A9" s="65" t="s">
+      <c r="I8" s="59"/>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="66" t="s">
+      <c r="C9" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="66">
+      <c r="D9" s="62">
         <v>5</v>
       </c>
       <c r="E9" s="31" t="s">
@@ -1384,15 +1387,15 @@
       <c r="H9" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="I9" s="61">
+      <c r="I9" s="64">
         <v>4.3486666669999998</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="16.149999999999999" thickBot="1">
-      <c r="A10" s="58"/>
-      <c r="B10" s="60"/>
-      <c r="C10" s="60"/>
-      <c r="D10" s="60"/>
+    <row r="10" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="61"/>
+      <c r="B10" s="63"/>
+      <c r="C10" s="63"/>
+      <c r="D10" s="63"/>
       <c r="E10" s="35" t="s">
         <v>15</v>
       </c>
@@ -1405,19 +1408,19 @@
       <c r="H10" s="38">
         <v>22.45</v>
       </c>
-      <c r="I10" s="62"/>
-    </row>
-    <row r="11" spans="1:9" ht="31.15">
-      <c r="A11" s="50" t="s">
+      <c r="I10" s="65"/>
+    </row>
+    <row r="11" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="52" t="s">
+      <c r="B11" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="52" t="s">
+      <c r="C11" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="52">
+      <c r="D11" s="56">
         <v>0.5</v>
       </c>
       <c r="E11" s="23" t="s">
@@ -1432,15 +1435,15 @@
       <c r="H11" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="I11" s="54">
+      <c r="I11" s="58">
         <v>25.126666669999999</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="16.149999999999999" thickBot="1">
-      <c r="A12" s="63"/>
-      <c r="B12" s="64"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
+    <row r="12" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="55"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
       <c r="E12" s="27" t="s">
         <v>15</v>
       </c>
@@ -1453,19 +1456,19 @@
       <c r="H12" s="30">
         <v>34.9</v>
       </c>
-      <c r="I12" s="56"/>
-    </row>
-    <row r="13" spans="1:9" ht="31.15">
-      <c r="A13" s="65" t="s">
+      <c r="I12" s="59"/>
+    </row>
+    <row r="13" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="66" t="s">
+      <c r="B13" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="66" t="s">
+      <c r="C13" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="66">
+      <c r="D13" s="62">
         <v>5</v>
       </c>
       <c r="E13" s="31" t="s">
@@ -1480,15 +1483,15 @@
       <c r="H13" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="61">
+      <c r="I13" s="64">
         <v>3.3180000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="16.149999999999999" thickBot="1">
-      <c r="A14" s="58"/>
-      <c r="B14" s="60"/>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
+    <row r="14" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="61"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
       <c r="E14" s="35" t="s">
         <v>15</v>
       </c>
@@ -1501,19 +1504,19 @@
       <c r="H14" s="38">
         <v>17.989999999999998</v>
       </c>
-      <c r="I14" s="62"/>
-    </row>
-    <row r="15" spans="1:9" ht="15.6">
-      <c r="A15" s="50" t="s">
+      <c r="I14" s="65"/>
+    </row>
+    <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="52" t="s">
+      <c r="B15" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="52" t="s">
+      <c r="C15" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="52">
+      <c r="D15" s="56">
         <v>1</v>
       </c>
       <c r="E15" s="23" t="s">
@@ -1528,15 +1531,15 @@
       <c r="H15" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="I15" s="54">
+      <c r="I15" s="58">
         <v>5.49</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="16.149999999999999" thickBot="1">
-      <c r="A16" s="63"/>
-      <c r="B16" s="64"/>
-      <c r="C16" s="64"/>
-      <c r="D16" s="64"/>
+    <row r="16" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="55"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
       <c r="E16" s="27" t="s">
         <v>15</v>
       </c>
@@ -1549,19 +1552,19 @@
       <c r="H16" s="30">
         <v>5.99</v>
       </c>
-      <c r="I16" s="56"/>
-    </row>
-    <row r="17" spans="1:9" ht="15.6">
-      <c r="A17" s="65" t="s">
+      <c r="I16" s="59"/>
+    </row>
+    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="66" t="s">
+      <c r="B17" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="66" t="s">
+      <c r="C17" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="66">
+      <c r="D17" s="62">
         <v>0.5</v>
       </c>
       <c r="E17" s="31" t="s">
@@ -1574,15 +1577,15 @@
         <v>36</v>
       </c>
       <c r="H17" s="34"/>
-      <c r="I17" s="61">
+      <c r="I17" s="64">
         <v>33.094999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="16.149999999999999" thickBot="1">
-      <c r="A18" s="58"/>
-      <c r="B18" s="60"/>
-      <c r="C18" s="60"/>
-      <c r="D18" s="60"/>
+    <row r="18" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="61"/>
+      <c r="B18" s="63"/>
+      <c r="C18" s="63"/>
+      <c r="D18" s="63"/>
       <c r="E18" s="35" t="s">
         <v>15</v>
       </c>
@@ -1593,19 +1596,19 @@
         <v>32.47</v>
       </c>
       <c r="H18" s="38"/>
-      <c r="I18" s="62"/>
-    </row>
-    <row r="19" spans="1:9" ht="15.6">
-      <c r="A19" s="50" t="s">
+      <c r="I18" s="65"/>
+    </row>
+    <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="52" t="s">
+      <c r="B19" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="52" t="s">
+      <c r="C19" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="52">
+      <c r="D19" s="56">
         <v>0.9</v>
       </c>
       <c r="E19" s="23" t="s">
@@ -1620,15 +1623,15 @@
       <c r="H19" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="I19" s="54">
+      <c r="I19" s="58">
         <v>7.2566666670000002</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="16.149999999999999" thickBot="1">
-      <c r="A20" s="63"/>
-      <c r="B20" s="64"/>
-      <c r="C20" s="64"/>
-      <c r="D20" s="64"/>
+    <row r="20" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="55"/>
+      <c r="B20" s="57"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
       <c r="E20" s="27" t="s">
         <v>15</v>
       </c>
@@ -1641,19 +1644,19 @@
       <c r="H20" s="30">
         <v>7.29</v>
       </c>
-      <c r="I20" s="56"/>
-    </row>
-    <row r="21" spans="1:9" ht="31.15">
-      <c r="A21" s="65" t="s">
+      <c r="I20" s="59"/>
+    </row>
+    <row r="21" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="66" t="s">
+      <c r="B21" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="66" t="s">
+      <c r="C21" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="D21" s="66">
+      <c r="D21" s="62">
         <v>1</v>
       </c>
       <c r="E21" s="31" t="s">
@@ -1668,15 +1671,15 @@
       <c r="H21" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="I21" s="61">
+      <c r="I21" s="64">
         <v>41.916666669999998</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="16.149999999999999" thickBot="1">
-      <c r="A22" s="58"/>
-      <c r="B22" s="60"/>
-      <c r="C22" s="60"/>
-      <c r="D22" s="60"/>
+    <row r="22" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="61"/>
+      <c r="B22" s="63"/>
+      <c r="C22" s="63"/>
+      <c r="D22" s="63"/>
       <c r="E22" s="35" t="s">
         <v>15</v>
       </c>
@@ -1689,19 +1692,19 @@
       <c r="H22" s="38">
         <v>43.95</v>
       </c>
-      <c r="I22" s="62"/>
-    </row>
-    <row r="23" spans="1:9" ht="15.6">
-      <c r="A23" s="50" t="s">
+      <c r="I22" s="65"/>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="52" t="s">
+      <c r="B23" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="C23" s="52" t="s">
+      <c r="C23" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="52">
+      <c r="D23" s="56">
         <v>1</v>
       </c>
       <c r="E23" s="23" t="s">
@@ -1710,15 +1713,15 @@
       <c r="F23" s="24"/>
       <c r="G23" s="25"/>
       <c r="H23" s="26"/>
-      <c r="I23" s="54">
+      <c r="I23" s="58">
         <v>13.9</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="16.149999999999999" thickBot="1">
-      <c r="A24" s="63"/>
-      <c r="B24" s="64"/>
-      <c r="C24" s="64"/>
-      <c r="D24" s="64"/>
+    <row r="24" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="55"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="57"/>
+      <c r="D24" s="57"/>
       <c r="E24" s="27" t="s">
         <v>15</v>
       </c>
@@ -1727,19 +1730,19 @@
       </c>
       <c r="G24" s="29"/>
       <c r="H24" s="30"/>
-      <c r="I24" s="56"/>
-    </row>
-    <row r="25" spans="1:9" ht="15.6">
-      <c r="A25" s="65" t="s">
+      <c r="I24" s="59"/>
+    </row>
+    <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="66" t="s">
+      <c r="B25" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="66" t="s">
+      <c r="C25" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="D25" s="66">
+      <c r="D25" s="62">
         <v>1</v>
       </c>
       <c r="E25" s="31" t="s">
@@ -1748,15 +1751,15 @@
       <c r="F25" s="42"/>
       <c r="G25" s="33"/>
       <c r="H25" s="34"/>
-      <c r="I25" s="61">
+      <c r="I25" s="64">
         <v>5.98</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="16.149999999999999" thickBot="1">
-      <c r="A26" s="58"/>
-      <c r="B26" s="60"/>
-      <c r="C26" s="60"/>
-      <c r="D26" s="60"/>
+    <row r="26" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="61"/>
+      <c r="B26" s="63"/>
+      <c r="C26" s="63"/>
+      <c r="D26" s="63"/>
       <c r="E26" s="35" t="s">
         <v>15</v>
       </c>
@@ -1765,19 +1768,19 @@
       </c>
       <c r="G26" s="37"/>
       <c r="H26" s="38"/>
-      <c r="I26" s="62"/>
-    </row>
-    <row r="27" spans="1:9" ht="16.149999999999999" thickBot="1">
-      <c r="A27" s="50" t="s">
+      <c r="I26" s="65"/>
+    </row>
+    <row r="27" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="52" t="s">
+      <c r="B27" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="52" t="s">
+      <c r="C27" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="52">
+      <c r="D27" s="56">
         <v>1</v>
       </c>
       <c r="E27" s="23" t="s">
@@ -1786,15 +1789,15 @@
       <c r="F27" s="46"/>
       <c r="G27" s="25"/>
       <c r="H27" s="26"/>
-      <c r="I27" s="54">
+      <c r="I27" s="58">
         <v>8.98</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="16.149999999999999" thickBot="1">
-      <c r="A28" s="51"/>
-      <c r="B28" s="53"/>
-      <c r="C28" s="53"/>
-      <c r="D28" s="53"/>
+    <row r="28" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="68"/>
+      <c r="B28" s="69"/>
+      <c r="C28" s="69"/>
+      <c r="D28" s="69"/>
       <c r="E28" s="27" t="s">
         <v>15</v>
       </c>
@@ -1803,19 +1806,19 @@
       </c>
       <c r="G28" s="29"/>
       <c r="H28" s="30"/>
-      <c r="I28" s="56"/>
-    </row>
-    <row r="29" spans="1:9" ht="15.6">
-      <c r="A29" s="57" t="s">
+      <c r="I28" s="59"/>
+    </row>
+    <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="B29" s="59" t="s">
+      <c r="B29" s="67" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="59" t="s">
+      <c r="C29" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="D29" s="59">
+      <c r="D29" s="67">
         <v>1</v>
       </c>
       <c r="E29" s="31" t="s">
@@ -1830,15 +1833,15 @@
       <c r="H29" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="I29" s="61">
+      <c r="I29" s="64">
         <v>5.29</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="16.149999999999999" thickBot="1">
-      <c r="A30" s="58"/>
-      <c r="B30" s="60"/>
-      <c r="C30" s="60"/>
-      <c r="D30" s="60"/>
+    <row r="30" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="61"/>
+      <c r="B30" s="63"/>
+      <c r="C30" s="63"/>
+      <c r="D30" s="63"/>
       <c r="E30" s="27" t="s">
         <v>15</v>
       </c>
@@ -1851,19 +1854,19 @@
       <c r="H30" s="49">
         <v>5.99</v>
       </c>
-      <c r="I30" s="62"/>
-    </row>
-    <row r="31" spans="1:9" ht="15.6">
-      <c r="A31" s="50" t="s">
+      <c r="I30" s="65"/>
+    </row>
+    <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="52" t="s">
+      <c r="B31" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="C31" s="52" t="s">
+      <c r="C31" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="52">
+      <c r="D31" s="56">
         <v>1</v>
       </c>
       <c r="E31" s="23" t="s">
@@ -1874,15 +1877,15 @@
       </c>
       <c r="G31" s="25"/>
       <c r="H31" s="26"/>
-      <c r="I31" s="54">
+      <c r="I31" s="58">
         <v>4.99</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="16.149999999999999" thickBot="1">
-      <c r="A32" s="51"/>
-      <c r="B32" s="53"/>
-      <c r="C32" s="53"/>
-      <c r="D32" s="53"/>
+    <row r="32" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="68"/>
+      <c r="B32" s="69"/>
+      <c r="C32" s="69"/>
+      <c r="D32" s="69"/>
       <c r="E32" s="27" t="s">
         <v>15</v>
       </c>
@@ -1891,10 +1894,71 @@
       </c>
       <c r="G32" s="29"/>
       <c r="H32" s="30"/>
-      <c r="I32" s="55"/>
+      <c r="I32" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="68">
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="I9:I10"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="E5:G5"/>
     <mergeCell ref="E6:H6"/>
@@ -1902,67 +1966,6 @@
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="I31:I32"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
